--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -1482,7 +1482,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
@@ -1594,7 +1594,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -1818,7 +1818,7 @@
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1930,7 +1930,7 @@
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2042,7 +2042,7 @@
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -2154,7 +2154,7 @@
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
@@ -2266,7 +2266,7 @@
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2714,7 +2714,7 @@
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
@@ -2938,7 +2938,7 @@
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
@@ -3050,7 +3050,7 @@
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3162,7 +3162,7 @@
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3498,7 +3498,7 @@
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3610,7 +3610,7 @@
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3722,7 +3722,7 @@
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
@@ -3834,7 +3834,7 @@
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
@@ -3946,7 +3946,7 @@
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4170,7 +4170,7 @@
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4282,7 +4282,7 @@
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
@@ -4506,7 +4506,7 @@
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4618,7 +4618,7 @@
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -4842,7 +4842,7 @@
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4954,7 +4954,7 @@
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -5066,7 +5066,7 @@
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
@@ -5178,7 +5178,7 @@
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -5290,7 +5290,7 @@
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -5514,7 +5514,7 @@
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
@@ -6211,7 +6211,7 @@
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
@@ -6323,7 +6323,7 @@
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -6435,7 +6435,7 @@
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -6547,7 +6547,7 @@
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
@@ -7015,7 +7015,7 @@
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
@@ -7132,7 +7132,7 @@
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
@@ -7249,7 +7249,7 @@
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -7366,7 +7366,7 @@
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -7600,7 +7600,7 @@
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
@@ -8072,7 +8072,7 @@
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>

--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ70"/>
+  <dimension ref="A1:AZ85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1494,48 +1494,48 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>135960741</v>
+        <v>135997945</v>
       </c>
       <c r="B9" t="n">
-        <v>79441</v>
+        <v>91834</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Kullsfjoten, Dlr</t>
+          <t>Hållindan, Dlr</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>452417</v>
+        <v>452360</v>
       </c>
       <c r="R9" t="n">
-        <v>6754099</v>
+        <v>6754236</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1559,22 +1559,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>09:14</t>
+          <t>18:32</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1589,65 +1589,65 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960741</t>
+          <t>https://artportalen.se/Sighting/135997945</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>135960743</v>
+        <v>135997950</v>
       </c>
       <c r="B10" t="n">
-        <v>79441</v>
+        <v>91834</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Kullsfjoten, Dlr</t>
+          <t>Hållindan, Dlr</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>452411</v>
+        <v>452390</v>
       </c>
       <c r="R10" t="n">
-        <v>6754135</v>
+        <v>6754233</v>
       </c>
       <c r="S10" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1671,22 +1671,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>09:18</t>
+          <t>18:59</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1701,65 +1701,65 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960743</t>
+          <t>https://artportalen.se/Sighting/135997950</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>135960744</v>
+        <v>135997951</v>
       </c>
       <c r="B11" t="n">
-        <v>79441</v>
+        <v>91834</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>3215</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rödgul trumpetsvamp</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Craterellus lutescens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Fr.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Kullsfjoten, Dlr</t>
+          <t>Hållindan, Dlr</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>452395</v>
+        <v>452372</v>
       </c>
       <c r="R11" t="n">
-        <v>6754106</v>
+        <v>6754176</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1783,22 +1783,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1813,24 +1813,24 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960744</t>
+          <t>https://artportalen.se/Sighting/135997951</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>135960745</v>
+        <v>135960741</v>
       </c>
       <c r="B12" t="n">
         <v>79441</v>
@@ -1865,10 +1865,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>452394</v>
+        <v>452417</v>
       </c>
       <c r="R12" t="n">
-        <v>6754098</v>
+        <v>6754099</v>
       </c>
       <c r="S12" t="n">
         <v>5</v>
@@ -1900,7 +1900,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1910,7 +1910,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>09:20</t>
+          <t>09:14</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1936,13 +1936,13 @@
       <c r="AY12" t="inlineStr"/>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960745</t>
+          <t>https://artportalen.se/Sighting/135960741</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>135960748</v>
+        <v>135960743</v>
       </c>
       <c r="B13" t="n">
         <v>79441</v>
@@ -1977,13 +1977,13 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>452363</v>
+        <v>452411</v>
       </c>
       <c r="R13" t="n">
-        <v>6754197</v>
+        <v>6754135</v>
       </c>
       <c r="S13" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T13" t="inlineStr">
         <is>
@@ -2012,7 +2012,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2022,7 +2022,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>09:33</t>
+          <t>09:18</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2048,13 +2048,13 @@
       <c r="AY13" t="inlineStr"/>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960748</t>
+          <t>https://artportalen.se/Sighting/135960743</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>135960750</v>
+        <v>135960744</v>
       </c>
       <c r="B14" t="n">
         <v>79441</v>
@@ -2089,13 +2089,13 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>452337</v>
+        <v>452395</v>
       </c>
       <c r="R14" t="n">
-        <v>6754209</v>
+        <v>6754106</v>
       </c>
       <c r="S14" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T14" t="inlineStr">
         <is>
@@ -2124,7 +2124,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2134,7 +2134,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>09:41</t>
+          <t>09:19</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2160,13 +2160,13 @@
       <c r="AY14" t="inlineStr"/>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960750</t>
+          <t>https://artportalen.se/Sighting/135960744</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>135960751</v>
+        <v>135960745</v>
       </c>
       <c r="B15" t="n">
         <v>79441</v>
@@ -2201,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>452340</v>
+        <v>452394</v>
       </c>
       <c r="R15" t="n">
-        <v>6754222</v>
+        <v>6754098</v>
       </c>
       <c r="S15" t="n">
         <v>5</v>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>09:46</t>
+          <t>09:20</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2272,13 +2272,13 @@
       <c r="AY15" t="inlineStr"/>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960751</t>
+          <t>https://artportalen.se/Sighting/135960745</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>135960758</v>
+        <v>135960748</v>
       </c>
       <c r="B16" t="n">
         <v>79441</v>
@@ -2313,13 +2313,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>452370</v>
+        <v>452363</v>
       </c>
       <c r="R16" t="n">
-        <v>6754290</v>
+        <v>6754197</v>
       </c>
       <c r="S16" t="n">
-        <v>57</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2358,7 +2358,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>10:10</t>
+          <t>09:33</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2384,13 +2384,13 @@
       <c r="AY16" t="inlineStr"/>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960758</t>
+          <t>https://artportalen.se/Sighting/135960748</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>135960759</v>
+        <v>135960750</v>
       </c>
       <c r="B17" t="n">
         <v>79441</v>
@@ -2425,13 +2425,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>452356</v>
+        <v>452337</v>
       </c>
       <c r="R17" t="n">
-        <v>6754300</v>
+        <v>6754209</v>
       </c>
       <c r="S17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2460,7 +2460,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>10:11</t>
+          <t>09:41</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2496,13 +2496,13 @@
       <c r="AY17" t="inlineStr"/>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960759</t>
+          <t>https://artportalen.se/Sighting/135960750</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>135960760</v>
+        <v>135960751</v>
       </c>
       <c r="B18" t="n">
         <v>79441</v>
@@ -2537,10 +2537,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>452346</v>
+        <v>452340</v>
       </c>
       <c r="R18" t="n">
-        <v>6754303</v>
+        <v>6754222</v>
       </c>
       <c r="S18" t="n">
         <v>5</v>
@@ -2572,7 +2572,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2582,7 +2582,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>10:12</t>
+          <t>09:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2608,13 +2608,13 @@
       <c r="AY18" t="inlineStr"/>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960760</t>
+          <t>https://artportalen.se/Sighting/135960751</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>135960762</v>
+        <v>135960758</v>
       </c>
       <c r="B19" t="n">
         <v>79441</v>
@@ -2649,13 +2649,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>452352</v>
+        <v>452370</v>
       </c>
       <c r="R19" t="n">
-        <v>6754316</v>
+        <v>6754290</v>
       </c>
       <c r="S19" t="n">
-        <v>6</v>
+        <v>57</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2694,7 +2694,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>10:14</t>
+          <t>10:10</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2720,13 +2720,13 @@
       <c r="AY19" t="inlineStr"/>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960762</t>
+          <t>https://artportalen.se/Sighting/135960758</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>135960763</v>
+        <v>135960759</v>
       </c>
       <c r="B20" t="n">
         <v>79441</v>
@@ -2761,13 +2761,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>452355</v>
+        <v>452356</v>
       </c>
       <c r="R20" t="n">
-        <v>6754319</v>
+        <v>6754300</v>
       </c>
       <c r="S20" t="n">
-        <v>17</v>
+        <v>6</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2796,7 +2796,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>10:15</t>
+          <t>10:11</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2832,13 +2832,13 @@
       <c r="AY20" t="inlineStr"/>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960763</t>
+          <t>https://artportalen.se/Sighting/135960759</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>135960764</v>
+        <v>135960760</v>
       </c>
       <c r="B21" t="n">
         <v>79441</v>
@@ -2873,13 +2873,13 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>452375</v>
+        <v>452346</v>
       </c>
       <c r="R21" t="n">
-        <v>6754294</v>
+        <v>6754303</v>
       </c>
       <c r="S21" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T21" t="inlineStr">
         <is>
@@ -2908,7 +2908,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2918,7 +2918,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>10:16</t>
+          <t>10:12</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2944,13 +2944,13 @@
       <c r="AY21" t="inlineStr"/>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960764</t>
+          <t>https://artportalen.se/Sighting/135960760</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>135960765</v>
+        <v>135960762</v>
       </c>
       <c r="B22" t="n">
         <v>79441</v>
@@ -2985,13 +2985,13 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>452389</v>
+        <v>452352</v>
       </c>
       <c r="R22" t="n">
-        <v>6754250</v>
+        <v>6754316</v>
       </c>
       <c r="S22" t="n">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -3020,7 +3020,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3030,7 +3030,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>10:22</t>
+          <t>10:14</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3056,13 +3056,13 @@
       <c r="AY22" t="inlineStr"/>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960765</t>
+          <t>https://artportalen.se/Sighting/135960762</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>135960766</v>
+        <v>135960763</v>
       </c>
       <c r="B23" t="n">
         <v>79441</v>
@@ -3097,13 +3097,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>452367</v>
+        <v>452355</v>
       </c>
       <c r="R23" t="n">
-        <v>6754247</v>
+        <v>6754319</v>
       </c>
       <c r="S23" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3132,7 +3132,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>10:29</t>
+          <t>10:15</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3168,13 +3168,13 @@
       <c r="AY23" t="inlineStr"/>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960766</t>
+          <t>https://artportalen.se/Sighting/135960763</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>135960767</v>
+        <v>135960764</v>
       </c>
       <c r="B24" t="n">
         <v>79441</v>
@@ -3209,13 +3209,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>452408</v>
+        <v>452375</v>
       </c>
       <c r="R24" t="n">
-        <v>6754238</v>
+        <v>6754294</v>
       </c>
       <c r="S24" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3244,7 +3244,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3254,7 +3254,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>10:35</t>
+          <t>10:16</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3280,13 +3280,13 @@
       <c r="AY24" t="inlineStr"/>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960767</t>
+          <t>https://artportalen.se/Sighting/135960764</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>135960769</v>
+        <v>135960765</v>
       </c>
       <c r="B25" t="n">
         <v>79441</v>
@@ -3321,13 +3321,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>452407</v>
+        <v>452389</v>
       </c>
       <c r="R25" t="n">
-        <v>6754231</v>
+        <v>6754250</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3356,7 +3356,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3366,7 +3366,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>10:38</t>
+          <t>10:22</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3392,13 +3392,13 @@
       <c r="AY25" t="inlineStr"/>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960769</t>
+          <t>https://artportalen.se/Sighting/135960765</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>135960771</v>
+        <v>135960766</v>
       </c>
       <c r="B26" t="n">
         <v>79441</v>
@@ -3433,13 +3433,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>452435</v>
+        <v>452367</v>
       </c>
       <c r="R26" t="n">
-        <v>6754205</v>
+        <v>6754247</v>
       </c>
       <c r="S26" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3468,7 +3468,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:29</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3504,13 +3504,13 @@
       <c r="AY26" t="inlineStr"/>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960771</t>
+          <t>https://artportalen.se/Sighting/135960766</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>135960772</v>
+        <v>135960767</v>
       </c>
       <c r="B27" t="n">
         <v>79441</v>
@@ -3545,10 +3545,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>452428</v>
+        <v>452408</v>
       </c>
       <c r="R27" t="n">
-        <v>6754218</v>
+        <v>6754238</v>
       </c>
       <c r="S27" t="n">
         <v>5</v>
@@ -3580,7 +3580,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3590,7 +3590,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>10:42</t>
+          <t>10:35</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3616,13 +3616,13 @@
       <c r="AY27" t="inlineStr"/>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960772</t>
+          <t>https://artportalen.se/Sighting/135960767</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>135960774</v>
+        <v>135960769</v>
       </c>
       <c r="B28" t="n">
         <v>79441</v>
@@ -3657,10 +3657,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>452433</v>
+        <v>452407</v>
       </c>
       <c r="R28" t="n">
-        <v>6754249</v>
+        <v>6754231</v>
       </c>
       <c r="S28" t="n">
         <v>5</v>
@@ -3692,7 +3692,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3702,7 +3702,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>10:44</t>
+          <t>10:38</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3728,13 +3728,13 @@
       <c r="AY28" t="inlineStr"/>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960774</t>
+          <t>https://artportalen.se/Sighting/135960769</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>135960775</v>
+        <v>135960771</v>
       </c>
       <c r="B29" t="n">
         <v>79441</v>
@@ -3769,10 +3769,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>452439</v>
+        <v>452435</v>
       </c>
       <c r="R29" t="n">
-        <v>6754277</v>
+        <v>6754205</v>
       </c>
       <c r="S29" t="n">
         <v>8</v>
@@ -3804,7 +3804,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3814,7 +3814,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>10:45</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3840,13 +3840,13 @@
       <c r="AY29" t="inlineStr"/>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960775</t>
+          <t>https://artportalen.se/Sighting/135960771</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>135960778</v>
+        <v>135960772</v>
       </c>
       <c r="B30" t="n">
         <v>79441</v>
@@ -3881,13 +3881,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>452463</v>
+        <v>452428</v>
       </c>
       <c r="R30" t="n">
-        <v>6754293</v>
+        <v>6754218</v>
       </c>
       <c r="S30" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3916,7 +3916,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3926,7 +3926,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>10:42</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3952,13 +3952,13 @@
       <c r="AY30" t="inlineStr"/>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960778</t>
+          <t>https://artportalen.se/Sighting/135960772</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>135960780</v>
+        <v>135960774</v>
       </c>
       <c r="B31" t="n">
         <v>79441</v>
@@ -3993,13 +3993,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>452483</v>
+        <v>452433</v>
       </c>
       <c r="R31" t="n">
-        <v>6754318</v>
+        <v>6754249</v>
       </c>
       <c r="S31" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4028,7 +4028,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4038,7 +4038,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>10:44</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4064,13 +4064,13 @@
       <c r="AY31" t="inlineStr"/>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960780</t>
+          <t>https://artportalen.se/Sighting/135960774</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>135960782</v>
+        <v>135960775</v>
       </c>
       <c r="B32" t="n">
         <v>79441</v>
@@ -4105,13 +4105,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>452502</v>
+        <v>452439</v>
       </c>
       <c r="R32" t="n">
-        <v>6754339</v>
+        <v>6754277</v>
       </c>
       <c r="S32" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4140,7 +4140,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -4150,7 +4150,7 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>11:38</t>
+          <t>10:45</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4176,13 +4176,13 @@
       <c r="AY32" t="inlineStr"/>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960782</t>
+          <t>https://artportalen.se/Sighting/135960775</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>135960783</v>
+        <v>135960778</v>
       </c>
       <c r="B33" t="n">
         <v>79441</v>
@@ -4217,13 +4217,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>452542</v>
+        <v>452463</v>
       </c>
       <c r="R33" t="n">
-        <v>6754348</v>
+        <v>6754293</v>
       </c>
       <c r="S33" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4252,7 +4252,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4262,7 +4262,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>11:50</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4288,13 +4288,13 @@
       <c r="AY33" t="inlineStr"/>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960783</t>
+          <t>https://artportalen.se/Sighting/135960778</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>135960784</v>
+        <v>135960780</v>
       </c>
       <c r="B34" t="n">
         <v>79441</v>
@@ -4329,13 +4329,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>452541</v>
+        <v>452483</v>
       </c>
       <c r="R34" t="n">
-        <v>6754350</v>
+        <v>6754318</v>
       </c>
       <c r="S34" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4364,7 +4364,7 @@
       </c>
       <c r="Z34" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
@@ -4374,7 +4374,7 @@
       </c>
       <c r="AB34" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4400,13 +4400,13 @@
       <c r="AY34" t="inlineStr"/>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960784</t>
+          <t>https://artportalen.se/Sighting/135960780</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>135960785</v>
+        <v>135960782</v>
       </c>
       <c r="B35" t="n">
         <v>79441</v>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>452520</v>
+        <v>452502</v>
       </c>
       <c r="R35" t="n">
-        <v>6754322</v>
+        <v>6754339</v>
       </c>
       <c r="S35" t="n">
         <v>7</v>
@@ -4476,7 +4476,7 @@
       </c>
       <c r="Z35" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AA35" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="AB35" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:38</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4512,13 +4512,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960785</t>
+          <t>https://artportalen.se/Sighting/135960782</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>135960786</v>
+        <v>135960783</v>
       </c>
       <c r="B36" t="n">
         <v>79441</v>
@@ -4553,10 +4553,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>452517</v>
+        <v>452542</v>
       </c>
       <c r="R36" t="n">
-        <v>6754321</v>
+        <v>6754348</v>
       </c>
       <c r="S36" t="n">
         <v>6</v>
@@ -4588,7 +4588,7 @@
       </c>
       <c r="Z36" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AA36" t="inlineStr">
@@ -4598,7 +4598,7 @@
       </c>
       <c r="AB36" t="inlineStr">
         <is>
-          <t>11:56</t>
+          <t>11:50</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4624,13 +4624,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960786</t>
+          <t>https://artportalen.se/Sighting/135960783</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>135960787</v>
+        <v>135960784</v>
       </c>
       <c r="B37" t="n">
         <v>79441</v>
@@ -4665,13 +4665,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>452515</v>
+        <v>452541</v>
       </c>
       <c r="R37" t="n">
-        <v>6754318</v>
+        <v>6754350</v>
       </c>
       <c r="S37" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
       </c>
       <c r="Z37" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA37" t="inlineStr">
@@ -4710,7 +4710,7 @@
       </c>
       <c r="AB37" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4736,13 +4736,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960787</t>
+          <t>https://artportalen.se/Sighting/135960784</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>135960788</v>
+        <v>135960785</v>
       </c>
       <c r="B38" t="n">
         <v>79441</v>
@@ -4777,13 +4777,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>452504</v>
+        <v>452520</v>
       </c>
       <c r="R38" t="n">
-        <v>6754306</v>
+        <v>6754322</v>
       </c>
       <c r="S38" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4812,7 +4812,7 @@
       </c>
       <c r="Z38" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA38" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="AB38" t="inlineStr">
         <is>
-          <t>11:57</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4848,13 +4848,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960788</t>
+          <t>https://artportalen.se/Sighting/135960785</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>135960789</v>
+        <v>135960786</v>
       </c>
       <c r="B39" t="n">
         <v>79441</v>
@@ -4889,13 +4889,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>452500</v>
+        <v>452517</v>
       </c>
       <c r="R39" t="n">
-        <v>6754301</v>
+        <v>6754321</v>
       </c>
       <c r="S39" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4924,7 +4924,7 @@
       </c>
       <c r="Z39" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AA39" t="inlineStr">
@@ -4934,7 +4934,7 @@
       </c>
       <c r="AB39" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:56</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4960,13 +4960,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960789</t>
+          <t>https://artportalen.se/Sighting/135960786</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>135960793</v>
+        <v>135960787</v>
       </c>
       <c r="B40" t="n">
         <v>79441</v>
@@ -5001,13 +5001,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>452463</v>
+        <v>452515</v>
       </c>
       <c r="R40" t="n">
-        <v>6754238</v>
+        <v>6754318</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -5036,7 +5036,7 @@
       </c>
       <c r="Z40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA40" t="inlineStr">
@@ -5046,7 +5046,7 @@
       </c>
       <c r="AB40" t="inlineStr">
         <is>
-          <t>12:20</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5072,13 +5072,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960793</t>
+          <t>https://artportalen.se/Sighting/135960787</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>135960797</v>
+        <v>135960788</v>
       </c>
       <c r="B41" t="n">
         <v>79441</v>
@@ -5113,13 +5113,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>452412</v>
+        <v>452504</v>
       </c>
       <c r="R41" t="n">
-        <v>6754226</v>
+        <v>6754306</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -5148,7 +5148,7 @@
       </c>
       <c r="Z41" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AA41" t="inlineStr">
@@ -5158,7 +5158,7 @@
       </c>
       <c r="AB41" t="inlineStr">
         <is>
-          <t>12:25</t>
+          <t>11:57</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5184,13 +5184,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960797</t>
+          <t>https://artportalen.se/Sighting/135960788</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>135960798</v>
+        <v>135960789</v>
       </c>
       <c r="B42" t="n">
         <v>79441</v>
@@ -5225,13 +5225,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>452394</v>
+        <v>452500</v>
       </c>
       <c r="R42" t="n">
-        <v>6754202</v>
+        <v>6754301</v>
       </c>
       <c r="S42" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5260,7 +5260,7 @@
       </c>
       <c r="Z42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA42" t="inlineStr">
@@ -5270,7 +5270,7 @@
       </c>
       <c r="AB42" t="inlineStr">
         <is>
-          <t>12:28</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5296,13 +5296,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960798</t>
+          <t>https://artportalen.se/Sighting/135960789</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>135960801</v>
+        <v>135960793</v>
       </c>
       <c r="B43" t="n">
         <v>79441</v>
@@ -5340,10 +5340,10 @@
         <v>452463</v>
       </c>
       <c r="R43" t="n">
-        <v>6754172</v>
+        <v>6754238</v>
       </c>
       <c r="S43" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5372,7 +5372,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5382,7 +5382,7 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>12:20</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5408,13 +5408,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960801</t>
+          <t>https://artportalen.se/Sighting/135960793</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>135960802</v>
+        <v>135960797</v>
       </c>
       <c r="B44" t="n">
         <v>79441</v>
@@ -5449,10 +5449,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>452444</v>
+        <v>452412</v>
       </c>
       <c r="R44" t="n">
-        <v>6754155</v>
+        <v>6754226</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5484,7 +5484,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5494,7 +5494,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>12:46</t>
+          <t>12:25</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5520,13 +5520,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960802</t>
+          <t>https://artportalen.se/Sighting/135960797</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>135961062</v>
+        <v>135960798</v>
       </c>
       <c r="B45" t="n">
         <v>79441</v>
@@ -5561,13 +5561,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>452425</v>
+        <v>452394</v>
       </c>
       <c r="R45" t="n">
-        <v>6754106</v>
+        <v>6754202</v>
       </c>
       <c r="S45" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5596,7 +5596,7 @@
       </c>
       <c r="Z45" t="inlineStr">
         <is>
-          <t>09:15</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AA45" t="inlineStr">
@@ -5606,12 +5606,7 @@
       </c>
       <c r="AB45" t="inlineStr">
         <is>
-          <t>09:15</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>På gran</t>
+          <t>12:28</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5626,24 +5621,24 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961062</t>
+          <t>https://artportalen.se/Sighting/135960798</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>135961071</v>
+        <v>135960801</v>
       </c>
       <c r="B46" t="n">
         <v>79441</v>
@@ -5678,13 +5673,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>452389</v>
+        <v>452463</v>
       </c>
       <c r="R46" t="n">
-        <v>6754270</v>
+        <v>6754172</v>
       </c>
       <c r="S46" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5713,7 +5708,7 @@
       </c>
       <c r="Z46" t="inlineStr">
         <is>
-          <t>10:13</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
@@ -5723,12 +5718,7 @@
       </c>
       <c r="AB46" t="inlineStr">
         <is>
-          <t>10:13</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På tallstam</t>
+          <t>12:42</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5743,24 +5733,24 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961071</t>
+          <t>https://artportalen.se/Sighting/135960801</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>135961077</v>
+        <v>135960802</v>
       </c>
       <c r="B47" t="n">
         <v>79441</v>
@@ -5795,13 +5785,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>452454</v>
+        <v>452444</v>
       </c>
       <c r="R47" t="n">
-        <v>6754309</v>
+        <v>6754155</v>
       </c>
       <c r="S47" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5830,7 +5820,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>10:40</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5840,12 +5830,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>10:40</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>På granaten</t>
+          <t>12:46</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5860,24 +5845,24 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961077</t>
+          <t>https://artportalen.se/Sighting/135960802</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>135961078</v>
+        <v>135961062</v>
       </c>
       <c r="B48" t="n">
         <v>79441</v>
@@ -5912,13 +5897,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>452480</v>
+        <v>452425</v>
       </c>
       <c r="R48" t="n">
-        <v>6754315</v>
+        <v>6754106</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5947,7 +5932,7 @@
       </c>
       <c r="Z48" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
@@ -5957,12 +5942,12 @@
       </c>
       <c r="AB48" t="inlineStr">
         <is>
-          <t>11:19</t>
+          <t>09:15</t>
         </is>
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>På grangren</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5988,13 +5973,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961078</t>
+          <t>https://artportalen.se/Sighting/135961062</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>135961081</v>
+        <v>135961071</v>
       </c>
       <c r="B49" t="n">
         <v>79441</v>
@@ -6029,10 +6014,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>452537</v>
+        <v>452389</v>
       </c>
       <c r="R49" t="n">
-        <v>6754322</v>
+        <v>6754270</v>
       </c>
       <c r="S49" t="n">
         <v>5</v>
@@ -6064,7 +6049,7 @@
       </c>
       <c r="Z49" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
@@ -6074,12 +6059,12 @@
       </c>
       <c r="AB49" t="inlineStr">
         <is>
-          <t>11:54</t>
+          <t>10:13</t>
         </is>
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>På grangrenar</t>
+          <t>På tallstam</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6105,38 +6090,38 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961081</t>
+          <t>https://artportalen.se/Sighting/135961071</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>135960749</v>
+        <v>135961077</v>
       </c>
       <c r="B50" t="n">
-        <v>79198</v>
+        <v>79441</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -6146,13 +6131,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>452367</v>
+        <v>452454</v>
       </c>
       <c r="R50" t="n">
-        <v>6754207</v>
+        <v>6754309</v>
       </c>
       <c r="S50" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -6181,7 +6166,7 @@
       </c>
       <c r="Z50" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:40</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
@@ -6191,7 +6176,12 @@
       </c>
       <c r="AB50" t="inlineStr">
         <is>
-          <t>09:37</t>
+          <t>10:40</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>På granaten</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6206,49 +6196,49 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960749</t>
+          <t>https://artportalen.se/Sighting/135961077</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>135960755</v>
+        <v>135961078</v>
       </c>
       <c r="B51" t="n">
-        <v>79198</v>
+        <v>79441</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6258,13 +6248,13 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>452389</v>
+        <v>452480</v>
       </c>
       <c r="R51" t="n">
-        <v>6754217</v>
+        <v>6754315</v>
       </c>
       <c r="S51" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -6293,7 +6283,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:19</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -6303,7 +6293,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>10:01</t>
+          <t>11:19</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>På grangren</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6318,49 +6313,49 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960755</t>
+          <t>https://artportalen.se/Sighting/135961078</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>135960757</v>
+        <v>135961081</v>
       </c>
       <c r="B52" t="n">
-        <v>79198</v>
+        <v>79441</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6370,13 +6365,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>452370</v>
+        <v>452537</v>
       </c>
       <c r="R52" t="n">
-        <v>6754290</v>
+        <v>6754322</v>
       </c>
       <c r="S52" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6405,7 +6400,7 @@
       </c>
       <c r="Z52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:54</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
@@ -6415,7 +6410,12 @@
       </c>
       <c r="AB52" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>11:54</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>På grangrenar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6430,24 +6430,24 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960757</t>
+          <t>https://artportalen.se/Sighting/135961081</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>135960768</v>
+        <v>135960749</v>
       </c>
       <c r="B53" t="n">
         <v>79198</v>
@@ -6482,13 +6482,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>452418</v>
+        <v>452367</v>
       </c>
       <c r="R53" t="n">
-        <v>6754237</v>
+        <v>6754207</v>
       </c>
       <c r="S53" t="n">
-        <v>24</v>
+        <v>7</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>10:37</t>
+          <t>09:37</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6553,13 +6553,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960768</t>
+          <t>https://artportalen.se/Sighting/135960749</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>135961064</v>
+        <v>135960755</v>
       </c>
       <c r="B54" t="n">
         <v>79198</v>
@@ -6594,13 +6594,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>452354</v>
+        <v>452389</v>
       </c>
       <c r="R54" t="n">
-        <v>6754155</v>
+        <v>6754217</v>
       </c>
       <c r="S54" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6629,7 +6629,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>09:26</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6639,12 +6639,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>09:26</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>10:01</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6659,24 +6654,24 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961064</t>
+          <t>https://artportalen.se/Sighting/135960755</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>135961079</v>
+        <v>135960757</v>
       </c>
       <c r="B55" t="n">
         <v>79198</v>
@@ -6711,13 +6706,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>452458</v>
+        <v>452370</v>
       </c>
       <c r="R55" t="n">
-        <v>6754291</v>
+        <v>6754290</v>
       </c>
       <c r="S55" t="n">
-        <v>23</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6746,7 +6741,7 @@
       </c>
       <c r="Z55" t="inlineStr">
         <is>
-          <t>11:28</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
@@ -6756,12 +6751,7 @@
       </c>
       <c r="AB55" t="inlineStr">
         <is>
-          <t>11:28</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>10:08</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6776,70 +6766,65 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961079</t>
+          <t>https://artportalen.se/Sighting/135960757</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>135960747</v>
+        <v>135960768</v>
       </c>
       <c r="B56" t="n">
-        <v>57977</v>
+        <v>79198</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P56" t="inlineStr">
         <is>
           <t>Kullsfjoten, Dlr</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>452373</v>
+        <v>452418</v>
       </c>
       <c r="R56" t="n">
-        <v>6754165</v>
+        <v>6754237</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>24</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6868,7 +6853,7 @@
       </c>
       <c r="Z56" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
@@ -6878,7 +6863,7 @@
       </c>
       <c r="AB56" t="inlineStr">
         <is>
-          <t>09:30</t>
+          <t>10:37</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6904,59 +6889,54 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960747</t>
+          <t>https://artportalen.se/Sighting/135960768</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>135960752</v>
+        <v>135961064</v>
       </c>
       <c r="B57" t="n">
-        <v>57977</v>
+        <v>79198</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P57" t="inlineStr">
         <is>
           <t>Kullsfjoten, Dlr</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>452343</v>
+        <v>452354</v>
       </c>
       <c r="R57" t="n">
-        <v>6754219</v>
+        <v>6754155</v>
       </c>
       <c r="S57" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6985,7 +6965,7 @@
       </c>
       <c r="Z57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:26</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
@@ -6995,7 +6975,12 @@
       </c>
       <c r="AB57" t="inlineStr">
         <is>
-          <t>09:47</t>
+          <t>09:26</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7010,70 +6995,65 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960752</t>
+          <t>https://artportalen.se/Sighting/135961064</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>135960754</v>
+        <v>135961079</v>
       </c>
       <c r="B58" t="n">
-        <v>57977</v>
+        <v>79198</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P58" t="inlineStr">
         <is>
           <t>Kullsfjoten, Dlr</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>452383</v>
+        <v>452458</v>
       </c>
       <c r="R58" t="n">
-        <v>6754215</v>
+        <v>6754291</v>
       </c>
       <c r="S58" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7102,7 +7082,7 @@
       </c>
       <c r="Z58" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:28</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
@@ -7112,7 +7092,12 @@
       </c>
       <c r="AB58" t="inlineStr">
         <is>
-          <t>09:57</t>
+          <t>11:28</t>
+        </is>
+      </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7127,70 +7112,65 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960754</t>
+          <t>https://artportalen.se/Sighting/135961079</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>135960779</v>
+        <v>135997942</v>
       </c>
       <c r="B59" t="n">
-        <v>57977</v>
+        <v>79200</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Kullsfjoten, Dlr</t>
+          <t>Hållindan, Dlr</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>452474</v>
+        <v>452416</v>
       </c>
       <c r="R59" t="n">
-        <v>6754317</v>
+        <v>6754129</v>
       </c>
       <c r="S59" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -7214,22 +7194,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB59" t="inlineStr">
         <is>
-          <t>11:31</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7244,70 +7224,65 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960779</t>
+          <t>https://artportalen.se/Sighting/135997942</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>135960753</v>
+        <v>135997943</v>
       </c>
       <c r="B60" t="n">
-        <v>57167</v>
+        <v>79200</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färsk spillning</t>
-        </is>
-      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Kullsfjoten, Dlr</t>
+          <t>Hållindan, Dlr</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>452375</v>
+        <v>452421</v>
       </c>
       <c r="R60" t="n">
-        <v>6754214</v>
+        <v>6754121</v>
       </c>
       <c r="S60" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -7331,22 +7306,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>18:22</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7361,65 +7336,65 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960753</t>
+          <t>https://artportalen.se/Sighting/135997943</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>135961068</v>
+        <v>135997944</v>
       </c>
       <c r="B61" t="n">
-        <v>57167</v>
+        <v>79200</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100138</v>
+        <v>6446</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Kullsfjoten, Dlr</t>
+          <t>Hållindan, Dlr</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>452345</v>
+        <v>452418</v>
       </c>
       <c r="R61" t="n">
-        <v>6754246</v>
+        <v>6754231</v>
       </c>
       <c r="S61" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7443,27 +7418,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>09:55</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>09:55</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Spillning</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7478,70 +7448,65 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961068</t>
+          <t>https://artportalen.se/Sighting/135997944</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>135960791</v>
+        <v>135997949</v>
       </c>
       <c r="B62" t="n">
-        <v>8461</v>
+        <v>79200</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Kullsfjoten, Dlr</t>
+          <t>Hållindan, Dlr</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>452466</v>
+        <v>452399</v>
       </c>
       <c r="R62" t="n">
-        <v>6754244</v>
+        <v>6754274</v>
       </c>
       <c r="S62" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7565,22 +7530,22 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB62" t="inlineStr">
         <is>
-          <t>12:15</t>
+          <t>18:53</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7595,62 +7560,62 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960791</t>
+          <t>https://artportalen.se/Sighting/135997949</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>135961080</v>
+        <v>135997957</v>
       </c>
       <c r="B63" t="n">
-        <v>8461</v>
+        <v>79200</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>106545</v>
+        <v>6446</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Kullsfjoten, Dlr</t>
+          <t>Hållindan, Dlr</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>452560</v>
+        <v>452517</v>
       </c>
       <c r="R63" t="n">
-        <v>6754374</v>
+        <v>6754296</v>
       </c>
       <c r="S63" t="n">
         <v>5</v>
@@ -7677,27 +7642,22 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>11:47</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>11:47</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Barklös tallåga</t>
+          <t>19:17</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7712,59 +7672,55 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961080</t>
+          <t>https://artportalen.se/Sighting/135997957</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>135960792</v>
+        <v>135960747</v>
       </c>
       <c r="B64" t="n">
-        <v>99276</v>
+        <v>57977</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J64" t="inlineStr">
-        <is>
-          <t>m²</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="M64" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -7773,13 +7729,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>452466</v>
+        <v>452373</v>
       </c>
       <c r="R64" t="n">
-        <v>6754244</v>
+        <v>6754165</v>
       </c>
       <c r="S64" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7808,7 +7764,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>12:18</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7818,12 +7774,7 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>12:18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>09:30</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7849,51 +7800,56 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960792</t>
+          <t>https://artportalen.se/Sighting/135960747</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>135961072</v>
+        <v>135960752</v>
       </c>
       <c r="B65" t="n">
-        <v>99276</v>
+        <v>57977</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
           <t>Kullsfjoten, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>452395</v>
+        <v>452343</v>
       </c>
       <c r="R65" t="n">
-        <v>6754251</v>
+        <v>6754219</v>
       </c>
       <c r="S65" t="n">
         <v>7</v>
@@ -7925,7 +7881,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>10:17</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7935,12 +7891,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>10:17</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Mossig barrblandskog. 15 st</t>
+          <t>09:47</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7955,65 +7906,70 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961072</t>
+          <t>https://artportalen.se/Sighting/135960752</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>135960756</v>
+        <v>135960754</v>
       </c>
       <c r="B66" t="n">
-        <v>79199</v>
+        <v>57977</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
+      <c r="M66" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Kullsfjoten, Dlr</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>452370</v>
+        <v>452383</v>
       </c>
       <c r="R66" t="n">
-        <v>6754290</v>
+        <v>6754215</v>
       </c>
       <c r="S66" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -8042,7 +7998,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8052,7 +8008,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>10:08</t>
+          <t>09:57</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8078,51 +8034,56 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135960756</t>
+          <t>https://artportalen.se/Sighting/135960754</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>135961063</v>
+        <v>135960779</v>
       </c>
       <c r="B67" t="n">
-        <v>79199</v>
+        <v>57977</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Kullsfjoten, Dlr</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>452428</v>
+        <v>452474</v>
       </c>
       <c r="R67" t="n">
-        <v>6754123</v>
+        <v>6754317</v>
       </c>
       <c r="S67" t="n">
         <v>5</v>
@@ -8154,7 +8115,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>09:19</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8164,12 +8125,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>09:19</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>11:31</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8184,65 +8140,69 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961063</t>
+          <t>https://artportalen.se/Sighting/135960779</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>135961066</v>
+        <v>135997952</v>
       </c>
       <c r="B68" t="n">
-        <v>79199</v>
+        <v>57979</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>228912</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr"/>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Kullsfjoten, Dlr</t>
+          <t>Hållindan, Dlr</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>452339</v>
+        <v>452369</v>
       </c>
       <c r="R68" t="n">
-        <v>6754241</v>
+        <v>6754174</v>
       </c>
       <c r="S68" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -8266,27 +8226,22 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>09:49</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2026-08-17</t>
+          <t>2026-08-18</t>
         </is>
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>09:49</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>19:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8301,65 +8256,70 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Maria Eriksson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961066</t>
+          <t>https://artportalen.se/Sighting/135997952</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>135961084</v>
+        <v>135960753</v>
       </c>
       <c r="B69" t="n">
-        <v>79199</v>
+        <v>57167</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>228912</v>
+        <v>100138</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
+      <c r="M69" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Kullsfjoten, Dlr</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>452419</v>
+        <v>452375</v>
       </c>
       <c r="R69" t="n">
-        <v>6754133</v>
+        <v>6754214</v>
       </c>
       <c r="S69" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -8388,7 +8348,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>12:42</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -8398,12 +8358,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>12:42</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Brandstubbe</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8418,49 +8373,49 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Ulf Lindenbaum</t>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135961084</t>
+          <t>https://artportalen.se/Sighting/135960753</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>135960790</v>
+        <v>135961068</v>
       </c>
       <c r="B70" t="n">
-        <v>80031</v>
+        <v>57167</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>229821</v>
+        <v>100138</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8470,10 +8425,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>452492</v>
+        <v>452345</v>
       </c>
       <c r="R70" t="n">
-        <v>6754303</v>
+        <v>6754246</v>
       </c>
       <c r="S70" t="n">
         <v>5</v>
@@ -8505,7 +8460,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:55</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8515,7 +8470,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>12:01</t>
+          <t>09:55</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Spillning</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8530,16 +8490,1750 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Håkan Thenander</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Håkan Thenander, Ulf Lindenbaum</t>
+          <t>Ulf Lindenbaum</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135961068</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>135997941</v>
+      </c>
+      <c r="B71" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Hållindan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>452347</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6754134</v>
+      </c>
+      <c r="S71" t="n">
+        <v>5</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:06</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Spillning</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135997941</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>135997948</v>
+      </c>
+      <c r="B72" t="n">
+        <v>57169</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>100138</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Tjäder</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Tetrao urogallus</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Hållindan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>452372</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6754287</v>
+      </c>
+      <c r="S72" t="n">
+        <v>5</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>18:51</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Spillning under tall</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135997948</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>135960791</v>
+      </c>
+      <c r="B73" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="M73" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Kullsfjoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>452466</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6754244</v>
+      </c>
+      <c r="S73" t="n">
+        <v>5</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>12:15</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135960791</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>135961080</v>
+      </c>
+      <c r="B74" t="n">
+        <v>8461</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Kullsfjoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>452560</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6754374</v>
+      </c>
+      <c r="S74" t="n">
+        <v>5</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>11:47</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>Barklös tallåga</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135961080</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>135997956</v>
+      </c>
+      <c r="B75" t="n">
+        <v>8463</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>106545</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Mindre märgborre</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Tomicus minor</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Hållindan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>452526</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6754248</v>
+      </c>
+      <c r="S75" t="n">
+        <v>7</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>19:17</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135997956</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>135960792</v>
+      </c>
+      <c r="B76" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Kullsfjoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>452466</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6754244</v>
+      </c>
+      <c r="S76" t="n">
+        <v>6</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>12:18</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135960792</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>135961072</v>
+      </c>
+      <c r="B77" t="n">
+        <v>99276</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Kullsfjoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>452395</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6754251</v>
+      </c>
+      <c r="S77" t="n">
+        <v>7</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>10:17</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Mossig barrblandskog. 15 st</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135961072</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>135960756</v>
+      </c>
+      <c r="B78" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Kullsfjoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>452370</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6754290</v>
+      </c>
+      <c r="S78" t="n">
+        <v>22</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>10:08</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135960756</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>135961063</v>
+      </c>
+      <c r="B79" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Kullsfjoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>452428</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6754123</v>
+      </c>
+      <c r="S79" t="n">
+        <v>5</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>09:19</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135961063</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>135961066</v>
+      </c>
+      <c r="B80" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Kullsfjoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>452339</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6754241</v>
+      </c>
+      <c r="S80" t="n">
+        <v>5</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>09:49</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135961066</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>135961084</v>
+      </c>
+      <c r="B81" t="n">
+        <v>79199</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Kullsfjoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>452419</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6754133</v>
+      </c>
+      <c r="S81" t="n">
+        <v>5</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Brandstubbe</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135961084</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>135997947</v>
+      </c>
+      <c r="B82" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Hållindan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>452356</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6754315</v>
+      </c>
+      <c r="S82" t="n">
+        <v>8</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>18:49</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135997947</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>135997953</v>
+      </c>
+      <c r="B83" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Hållindan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>452497</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6754211</v>
+      </c>
+      <c r="S83" t="n">
+        <v>5</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>19:12</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135997953</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>135997958</v>
+      </c>
+      <c r="B84" t="n">
+        <v>79201</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>228912</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Mörk kolflarnlav</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Carbonicola myrmecina</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Hållindan, Dlr</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>452515</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6754275</v>
+      </c>
+      <c r="S84" t="n">
+        <v>8</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2026-08-18</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Maria Eriksson</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135997958</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>135960790</v>
+      </c>
+      <c r="B85" t="n">
+        <v>80031</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Kullsfjoten, Dlr</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>452492</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6754303</v>
+      </c>
+      <c r="S85" t="n">
+        <v>5</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Mora</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2026-08-17</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>12:01</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Håkan Thenander, Ulf Lindenbaum</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/135960790</t>
         </is>
@@ -8616,6 +10310,21 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135961065</v>
       </c>
       <c r="B2" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135961070</v>
       </c>
       <c r="B3" t="n">
-        <v>79473</v>
+        <v>79475</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135961067</v>
       </c>
       <c r="B4" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135961069</v>
       </c>
       <c r="B5" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135961082</v>
       </c>
       <c r="B6" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135961083</v>
       </c>
       <c r="B7" t="n">
-        <v>79107</v>
+        <v>79109</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135960777</v>
       </c>
       <c r="B8" t="n">
-        <v>92264</v>
+        <v>92278</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>135960741</v>
       </c>
       <c r="B12" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135960743</v>
       </c>
       <c r="B13" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>135960744</v>
       </c>
       <c r="B14" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>135960745</v>
       </c>
       <c r="B15" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135960748</v>
       </c>
       <c r="B16" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>135960750</v>
       </c>
       <c r="B17" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>135960751</v>
       </c>
       <c r="B18" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135960758</v>
       </c>
       <c r="B19" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>135960759</v>
       </c>
       <c r="B20" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135960760</v>
       </c>
       <c r="B21" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>135960762</v>
       </c>
       <c r="B22" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135960763</v>
       </c>
       <c r="B23" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135960764</v>
       </c>
       <c r="B24" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>135960765</v>
       </c>
       <c r="B25" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>135960766</v>
       </c>
       <c r="B26" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135960767</v>
       </c>
       <c r="B27" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135960769</v>
       </c>
       <c r="B28" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>135960771</v>
       </c>
       <c r="B29" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135960772</v>
       </c>
       <c r="B30" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>135960774</v>
       </c>
       <c r="B31" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>135960775</v>
       </c>
       <c r="B32" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>135960778</v>
       </c>
       <c r="B33" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135960780</v>
       </c>
       <c r="B34" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135960782</v>
       </c>
       <c r="B35" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135960783</v>
       </c>
       <c r="B36" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135960784</v>
       </c>
       <c r="B37" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135960785</v>
       </c>
       <c r="B38" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135960786</v>
       </c>
       <c r="B39" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135960787</v>
       </c>
       <c r="B40" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>135960788</v>
       </c>
       <c r="B41" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>135960789</v>
       </c>
       <c r="B42" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>135960793</v>
       </c>
       <c r="B43" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135960797</v>
       </c>
       <c r="B44" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135960798</v>
       </c>
       <c r="B45" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135960801</v>
       </c>
       <c r="B46" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135960802</v>
       </c>
       <c r="B47" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135961062</v>
       </c>
       <c r="B48" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>135961071</v>
       </c>
       <c r="B49" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>135961077</v>
       </c>
       <c r="B50" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>135961078</v>
       </c>
       <c r="B51" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>135961081</v>
       </c>
       <c r="B52" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>135960749</v>
       </c>
       <c r="B53" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>135960755</v>
       </c>
       <c r="B54" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>135960757</v>
       </c>
       <c r="B55" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135960768</v>
       </c>
       <c r="B56" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135961064</v>
       </c>
       <c r="B57" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>135961079</v>
       </c>
       <c r="B58" t="n">
-        <v>79198</v>
+        <v>79200</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>135960747</v>
       </c>
       <c r="B64" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>135960752</v>
       </c>
       <c r="B65" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135960754</v>
       </c>
       <c r="B66" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>135960779</v>
       </c>
       <c r="B67" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135960753</v>
       </c>
       <c r="B69" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>135961068</v>
       </c>
       <c r="B70" t="n">
-        <v>57167</v>
+        <v>57169</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8744,7 +8744,7 @@
         <v>135960791</v>
       </c>
       <c r="B73" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8861,7 +8861,7 @@
         <v>135961080</v>
       </c>
       <c r="B74" t="n">
-        <v>8461</v>
+        <v>8463</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>135960792</v>
       </c>
       <c r="B76" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>135961072</v>
       </c>
       <c r="B77" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135960756</v>
       </c>
       <c r="B78" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>135961063</v>
       </c>
       <c r="B79" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135961066</v>
       </c>
       <c r="B80" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>135961084</v>
       </c>
       <c r="B81" t="n">
-        <v>79199</v>
+        <v>79201</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135960790</v>
       </c>
       <c r="B85" t="n">
-        <v>80031</v>
+        <v>80033</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135961065</v>
       </c>
       <c r="B2" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135961070</v>
       </c>
       <c r="B3" t="n">
-        <v>79475</v>
+        <v>79476</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135961067</v>
       </c>
       <c r="B4" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135961069</v>
       </c>
       <c r="B5" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135961082</v>
       </c>
       <c r="B6" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135961083</v>
       </c>
       <c r="B7" t="n">
-        <v>79109</v>
+        <v>79110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135960777</v>
       </c>
       <c r="B8" t="n">
-        <v>92278</v>
+        <v>92279</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135997945</v>
       </c>
       <c r="B9" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>135997950</v>
       </c>
       <c r="B10" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135997951</v>
       </c>
       <c r="B11" t="n">
-        <v>91834</v>
+        <v>91835</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>135960741</v>
       </c>
       <c r="B12" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135960743</v>
       </c>
       <c r="B13" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>135960744</v>
       </c>
       <c r="B14" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>135960745</v>
       </c>
       <c r="B15" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135960748</v>
       </c>
       <c r="B16" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>135960750</v>
       </c>
       <c r="B17" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>135960751</v>
       </c>
       <c r="B18" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135960758</v>
       </c>
       <c r="B19" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>135960759</v>
       </c>
       <c r="B20" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135960760</v>
       </c>
       <c r="B21" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>135960762</v>
       </c>
       <c r="B22" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135960763</v>
       </c>
       <c r="B23" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135960764</v>
       </c>
       <c r="B24" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>135960765</v>
       </c>
       <c r="B25" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>135960766</v>
       </c>
       <c r="B26" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135960767</v>
       </c>
       <c r="B27" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135960769</v>
       </c>
       <c r="B28" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>135960771</v>
       </c>
       <c r="B29" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135960772</v>
       </c>
       <c r="B30" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>135960774</v>
       </c>
       <c r="B31" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>135960775</v>
       </c>
       <c r="B32" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>135960778</v>
       </c>
       <c r="B33" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135960780</v>
       </c>
       <c r="B34" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135960782</v>
       </c>
       <c r="B35" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135960783</v>
       </c>
       <c r="B36" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135960784</v>
       </c>
       <c r="B37" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135960785</v>
       </c>
       <c r="B38" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135960786</v>
       </c>
       <c r="B39" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135960787</v>
       </c>
       <c r="B40" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>135960788</v>
       </c>
       <c r="B41" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>135960789</v>
       </c>
       <c r="B42" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>135960793</v>
       </c>
       <c r="B43" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135960797</v>
       </c>
       <c r="B44" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135960798</v>
       </c>
       <c r="B45" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135960801</v>
       </c>
       <c r="B46" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135960802</v>
       </c>
       <c r="B47" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135961062</v>
       </c>
       <c r="B48" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>135961071</v>
       </c>
       <c r="B49" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>135961077</v>
       </c>
       <c r="B50" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>135961078</v>
       </c>
       <c r="B51" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>135961081</v>
       </c>
       <c r="B52" t="n">
-        <v>79443</v>
+        <v>79444</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>135960749</v>
       </c>
       <c r="B53" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>135960755</v>
       </c>
       <c r="B54" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>135960757</v>
       </c>
       <c r="B55" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135960768</v>
       </c>
       <c r="B56" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135961064</v>
       </c>
       <c r="B57" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>135961079</v>
       </c>
       <c r="B58" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>135997942</v>
       </c>
       <c r="B59" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>135997943</v>
       </c>
       <c r="B60" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135997944</v>
       </c>
       <c r="B61" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>135997949</v>
       </c>
       <c r="B62" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>135997957</v>
       </c>
       <c r="B63" t="n">
-        <v>79200</v>
+        <v>79201</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>135960792</v>
       </c>
       <c r="B76" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>135961072</v>
       </c>
       <c r="B77" t="n">
-        <v>99293</v>
+        <v>99294</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135960756</v>
       </c>
       <c r="B78" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>135961063</v>
       </c>
       <c r="B79" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135961066</v>
       </c>
       <c r="B80" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>135961084</v>
       </c>
       <c r="B81" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>135997947</v>
       </c>
       <c r="B82" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>135997953</v>
       </c>
       <c r="B83" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>135997958</v>
       </c>
       <c r="B84" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135960790</v>
       </c>
       <c r="B85" t="n">
-        <v>80033</v>
+        <v>80034</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -1385,7 +1385,7 @@
         <v>135960777</v>
       </c>
       <c r="B8" t="n">
-        <v>92279</v>
+        <v>92280</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135997945</v>
       </c>
       <c r="B9" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>135997950</v>
       </c>
       <c r="B10" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135997951</v>
       </c>
       <c r="B11" t="n">
-        <v>91835</v>
+        <v>91836</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>135960792</v>
       </c>
       <c r="B76" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>135961072</v>
       </c>
       <c r="B77" t="n">
-        <v>99294</v>
+        <v>99295</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>

--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135961065</v>
       </c>
       <c r="B2" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135961070</v>
       </c>
       <c r="B3" t="n">
-        <v>79476</v>
+        <v>79477</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135961067</v>
       </c>
       <c r="B4" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135961069</v>
       </c>
       <c r="B5" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135961082</v>
       </c>
       <c r="B6" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135961083</v>
       </c>
       <c r="B7" t="n">
-        <v>79110</v>
+        <v>79111</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135960777</v>
       </c>
       <c r="B8" t="n">
-        <v>92280</v>
+        <v>92281</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135997945</v>
       </c>
       <c r="B9" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>135997950</v>
       </c>
       <c r="B10" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135997951</v>
       </c>
       <c r="B11" t="n">
-        <v>91836</v>
+        <v>91837</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>135960741</v>
       </c>
       <c r="B12" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135960743</v>
       </c>
       <c r="B13" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>135960744</v>
       </c>
       <c r="B14" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>135960745</v>
       </c>
       <c r="B15" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135960748</v>
       </c>
       <c r="B16" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>135960750</v>
       </c>
       <c r="B17" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>135960751</v>
       </c>
       <c r="B18" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135960758</v>
       </c>
       <c r="B19" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>135960759</v>
       </c>
       <c r="B20" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135960760</v>
       </c>
       <c r="B21" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>135960762</v>
       </c>
       <c r="B22" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135960763</v>
       </c>
       <c r="B23" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135960764</v>
       </c>
       <c r="B24" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>135960765</v>
       </c>
       <c r="B25" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>135960766</v>
       </c>
       <c r="B26" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135960767</v>
       </c>
       <c r="B27" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135960769</v>
       </c>
       <c r="B28" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>135960771</v>
       </c>
       <c r="B29" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135960772</v>
       </c>
       <c r="B30" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>135960774</v>
       </c>
       <c r="B31" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>135960775</v>
       </c>
       <c r="B32" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>135960778</v>
       </c>
       <c r="B33" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135960780</v>
       </c>
       <c r="B34" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135960782</v>
       </c>
       <c r="B35" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135960783</v>
       </c>
       <c r="B36" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135960784</v>
       </c>
       <c r="B37" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135960785</v>
       </c>
       <c r="B38" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135960786</v>
       </c>
       <c r="B39" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135960787</v>
       </c>
       <c r="B40" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>135960788</v>
       </c>
       <c r="B41" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>135960789</v>
       </c>
       <c r="B42" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>135960793</v>
       </c>
       <c r="B43" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135960797</v>
       </c>
       <c r="B44" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135960798</v>
       </c>
       <c r="B45" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135960801</v>
       </c>
       <c r="B46" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135960802</v>
       </c>
       <c r="B47" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135961062</v>
       </c>
       <c r="B48" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>135961071</v>
       </c>
       <c r="B49" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>135961077</v>
       </c>
       <c r="B50" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>135961078</v>
       </c>
       <c r="B51" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>135961081</v>
       </c>
       <c r="B52" t="n">
-        <v>79444</v>
+        <v>79445</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>135960749</v>
       </c>
       <c r="B53" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>135960755</v>
       </c>
       <c r="B54" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>135960757</v>
       </c>
       <c r="B55" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135960768</v>
       </c>
       <c r="B56" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135961064</v>
       </c>
       <c r="B57" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>135961079</v>
       </c>
       <c r="B58" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>135997942</v>
       </c>
       <c r="B59" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>135997943</v>
       </c>
       <c r="B60" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135997944</v>
       </c>
       <c r="B61" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>135997949</v>
       </c>
       <c r="B62" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>135997957</v>
       </c>
       <c r="B63" t="n">
-        <v>79201</v>
+        <v>79202</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>135960747</v>
       </c>
       <c r="B64" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>135960752</v>
       </c>
       <c r="B65" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135960754</v>
       </c>
       <c r="B66" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>135960779</v>
       </c>
       <c r="B67" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>135997952</v>
       </c>
       <c r="B68" t="n">
-        <v>57979</v>
+        <v>57980</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135960753</v>
       </c>
       <c r="B69" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>135961068</v>
       </c>
       <c r="B70" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>135997941</v>
       </c>
       <c r="B71" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135997948</v>
       </c>
       <c r="B72" t="n">
-        <v>57169</v>
+        <v>57170</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>135960792</v>
       </c>
       <c r="B76" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>135961072</v>
       </c>
       <c r="B77" t="n">
-        <v>99295</v>
+        <v>99296</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135960756</v>
       </c>
       <c r="B78" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>135961063</v>
       </c>
       <c r="B79" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135961066</v>
       </c>
       <c r="B80" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>135961084</v>
       </c>
       <c r="B81" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>135997947</v>
       </c>
       <c r="B82" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>135997953</v>
       </c>
       <c r="B83" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>135997958</v>
       </c>
       <c r="B84" t="n">
-        <v>79202</v>
+        <v>79203</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135960790</v>
       </c>
       <c r="B85" t="n">
-        <v>80034</v>
+        <v>80035</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135961065</v>
       </c>
       <c r="B2" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135961070</v>
       </c>
       <c r="B3" t="n">
-        <v>79477</v>
+        <v>79481</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135961067</v>
       </c>
       <c r="B4" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135961069</v>
       </c>
       <c r="B5" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135961082</v>
       </c>
       <c r="B6" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135961083</v>
       </c>
       <c r="B7" t="n">
-        <v>79111</v>
+        <v>79115</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135960777</v>
       </c>
       <c r="B8" t="n">
-        <v>92281</v>
+        <v>92287</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135997945</v>
       </c>
       <c r="B9" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>135997950</v>
       </c>
       <c r="B10" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135997951</v>
       </c>
       <c r="B11" t="n">
-        <v>91837</v>
+        <v>91843</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>135960741</v>
       </c>
       <c r="B12" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135960743</v>
       </c>
       <c r="B13" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>135960744</v>
       </c>
       <c r="B14" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>135960745</v>
       </c>
       <c r="B15" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135960748</v>
       </c>
       <c r="B16" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>135960750</v>
       </c>
       <c r="B17" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>135960751</v>
       </c>
       <c r="B18" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135960758</v>
       </c>
       <c r="B19" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>135960759</v>
       </c>
       <c r="B20" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135960760</v>
       </c>
       <c r="B21" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>135960762</v>
       </c>
       <c r="B22" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135960763</v>
       </c>
       <c r="B23" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135960764</v>
       </c>
       <c r="B24" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>135960765</v>
       </c>
       <c r="B25" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>135960766</v>
       </c>
       <c r="B26" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135960767</v>
       </c>
       <c r="B27" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135960769</v>
       </c>
       <c r="B28" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>135960771</v>
       </c>
       <c r="B29" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135960772</v>
       </c>
       <c r="B30" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>135960774</v>
       </c>
       <c r="B31" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>135960775</v>
       </c>
       <c r="B32" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>135960778</v>
       </c>
       <c r="B33" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135960780</v>
       </c>
       <c r="B34" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135960782</v>
       </c>
       <c r="B35" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135960783</v>
       </c>
       <c r="B36" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135960784</v>
       </c>
       <c r="B37" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135960785</v>
       </c>
       <c r="B38" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135960786</v>
       </c>
       <c r="B39" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135960787</v>
       </c>
       <c r="B40" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>135960788</v>
       </c>
       <c r="B41" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>135960789</v>
       </c>
       <c r="B42" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>135960793</v>
       </c>
       <c r="B43" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135960797</v>
       </c>
       <c r="B44" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135960798</v>
       </c>
       <c r="B45" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135960801</v>
       </c>
       <c r="B46" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135960802</v>
       </c>
       <c r="B47" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135961062</v>
       </c>
       <c r="B48" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>135961071</v>
       </c>
       <c r="B49" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>135961077</v>
       </c>
       <c r="B50" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>135961078</v>
       </c>
       <c r="B51" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>135961081</v>
       </c>
       <c r="B52" t="n">
-        <v>79445</v>
+        <v>79449</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>135960749</v>
       </c>
       <c r="B53" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>135960755</v>
       </c>
       <c r="B54" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>135960757</v>
       </c>
       <c r="B55" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135960768</v>
       </c>
       <c r="B56" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135961064</v>
       </c>
       <c r="B57" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>135961079</v>
       </c>
       <c r="B58" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>135997942</v>
       </c>
       <c r="B59" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>135997943</v>
       </c>
       <c r="B60" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135997944</v>
       </c>
       <c r="B61" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>135997949</v>
       </c>
       <c r="B62" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>135997957</v>
       </c>
       <c r="B63" t="n">
-        <v>79202</v>
+        <v>79206</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>135960747</v>
       </c>
       <c r="B64" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>135960752</v>
       </c>
       <c r="B65" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135960754</v>
       </c>
       <c r="B66" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>135960779</v>
       </c>
       <c r="B67" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>135997952</v>
       </c>
       <c r="B68" t="n">
-        <v>57980</v>
+        <v>57984</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135960753</v>
       </c>
       <c r="B69" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>135961068</v>
       </c>
       <c r="B70" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>135997941</v>
       </c>
       <c r="B71" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135997948</v>
       </c>
       <c r="B72" t="n">
-        <v>57170</v>
+        <v>57174</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>135960792</v>
       </c>
       <c r="B76" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>135961072</v>
       </c>
       <c r="B77" t="n">
-        <v>99296</v>
+        <v>99302</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135960756</v>
       </c>
       <c r="B78" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>135961063</v>
       </c>
       <c r="B79" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135961066</v>
       </c>
       <c r="B80" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>135961084</v>
       </c>
       <c r="B81" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>135997947</v>
       </c>
       <c r="B82" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>135997953</v>
       </c>
       <c r="B83" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>135997958</v>
       </c>
       <c r="B84" t="n">
-        <v>79203</v>
+        <v>79207</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135960790</v>
       </c>
       <c r="B85" t="n">
-        <v>80035</v>
+        <v>80039</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>

--- a/artfynd/A 29865-2026 artfynd.xlsx
+++ b/artfynd/A 29865-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135961065</v>
       </c>
       <c r="B2" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -800,7 +800,7 @@
         <v>135961070</v>
       </c>
       <c r="B3" t="n">
-        <v>79481</v>
+        <v>79482</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135961067</v>
       </c>
       <c r="B4" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1034,7 +1034,7 @@
         <v>135961069</v>
       </c>
       <c r="B5" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>135961082</v>
       </c>
       <c r="B6" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135961083</v>
       </c>
       <c r="B7" t="n">
-        <v>79115</v>
+        <v>79116</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,7 +1385,7 @@
         <v>135960777</v>
       </c>
       <c r="B8" t="n">
-        <v>92287</v>
+        <v>92288</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1497,7 +1497,7 @@
         <v>135997945</v>
       </c>
       <c r="B9" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>135997950</v>
       </c>
       <c r="B10" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1721,7 +1721,7 @@
         <v>135997951</v>
       </c>
       <c r="B11" t="n">
-        <v>91843</v>
+        <v>91844</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1833,7 +1833,7 @@
         <v>135960741</v>
       </c>
       <c r="B12" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1945,7 +1945,7 @@
         <v>135960743</v>
       </c>
       <c r="B13" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2057,7 +2057,7 @@
         <v>135960744</v>
       </c>
       <c r="B14" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2169,7 +2169,7 @@
         <v>135960745</v>
       </c>
       <c r="B15" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2281,7 +2281,7 @@
         <v>135960748</v>
       </c>
       <c r="B16" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2393,7 +2393,7 @@
         <v>135960750</v>
       </c>
       <c r="B17" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2505,7 +2505,7 @@
         <v>135960751</v>
       </c>
       <c r="B18" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2617,7 +2617,7 @@
         <v>135960758</v>
       </c>
       <c r="B19" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2729,7 +2729,7 @@
         <v>135960759</v>
       </c>
       <c r="B20" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2841,7 +2841,7 @@
         <v>135960760</v>
       </c>
       <c r="B21" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2953,7 +2953,7 @@
         <v>135960762</v>
       </c>
       <c r="B22" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -3065,7 +3065,7 @@
         <v>135960763</v>
       </c>
       <c r="B23" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3177,7 +3177,7 @@
         <v>135960764</v>
       </c>
       <c r="B24" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3289,7 +3289,7 @@
         <v>135960765</v>
       </c>
       <c r="B25" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3401,7 +3401,7 @@
         <v>135960766</v>
       </c>
       <c r="B26" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3513,7 +3513,7 @@
         <v>135960767</v>
       </c>
       <c r="B27" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>135960769</v>
       </c>
       <c r="B28" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3737,7 +3737,7 @@
         <v>135960771</v>
       </c>
       <c r="B29" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3849,7 +3849,7 @@
         <v>135960772</v>
       </c>
       <c r="B30" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3961,7 +3961,7 @@
         <v>135960774</v>
       </c>
       <c r="B31" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4073,7 +4073,7 @@
         <v>135960775</v>
       </c>
       <c r="B32" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4185,7 +4185,7 @@
         <v>135960778</v>
       </c>
       <c r="B33" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4297,7 +4297,7 @@
         <v>135960780</v>
       </c>
       <c r="B34" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>135960782</v>
       </c>
       <c r="B35" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4521,7 +4521,7 @@
         <v>135960783</v>
       </c>
       <c r="B36" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4633,7 +4633,7 @@
         <v>135960784</v>
       </c>
       <c r="B37" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4745,7 +4745,7 @@
         <v>135960785</v>
       </c>
       <c r="B38" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4857,7 +4857,7 @@
         <v>135960786</v>
       </c>
       <c r="B39" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4969,7 +4969,7 @@
         <v>135960787</v>
       </c>
       <c r="B40" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -5081,7 +5081,7 @@
         <v>135960788</v>
       </c>
       <c r="B41" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5193,7 +5193,7 @@
         <v>135960789</v>
       </c>
       <c r="B42" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5305,7 +5305,7 @@
         <v>135960793</v>
       </c>
       <c r="B43" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5417,7 +5417,7 @@
         <v>135960797</v>
       </c>
       <c r="B44" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5529,7 +5529,7 @@
         <v>135960798</v>
       </c>
       <c r="B45" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5641,7 +5641,7 @@
         <v>135960801</v>
       </c>
       <c r="B46" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5753,7 +5753,7 @@
         <v>135960802</v>
       </c>
       <c r="B47" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5865,7 +5865,7 @@
         <v>135961062</v>
       </c>
       <c r="B48" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5982,7 +5982,7 @@
         <v>135961071</v>
       </c>
       <c r="B49" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -6099,7 +6099,7 @@
         <v>135961077</v>
       </c>
       <c r="B50" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6216,7 +6216,7 @@
         <v>135961078</v>
       </c>
       <c r="B51" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6333,7 +6333,7 @@
         <v>135961081</v>
       </c>
       <c r="B52" t="n">
-        <v>79449</v>
+        <v>79450</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6450,7 +6450,7 @@
         <v>135960749</v>
       </c>
       <c r="B53" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6562,7 +6562,7 @@
         <v>135960755</v>
       </c>
       <c r="B54" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6674,7 +6674,7 @@
         <v>135960757</v>
       </c>
       <c r="B55" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6786,7 +6786,7 @@
         <v>135960768</v>
       </c>
       <c r="B56" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6898,7 +6898,7 @@
         <v>135961064</v>
       </c>
       <c r="B57" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -7015,7 +7015,7 @@
         <v>135961079</v>
       </c>
       <c r="B58" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -7132,7 +7132,7 @@
         <v>135997942</v>
       </c>
       <c r="B59" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -7244,7 +7244,7 @@
         <v>135997943</v>
       </c>
       <c r="B60" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -7356,7 +7356,7 @@
         <v>135997944</v>
       </c>
       <c r="B61" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7468,7 +7468,7 @@
         <v>135997949</v>
       </c>
       <c r="B62" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7580,7 +7580,7 @@
         <v>135997957</v>
       </c>
       <c r="B63" t="n">
-        <v>79206</v>
+        <v>79207</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7692,7 +7692,7 @@
         <v>135960747</v>
       </c>
       <c r="B64" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7809,7 +7809,7 @@
         <v>135960752</v>
       </c>
       <c r="B65" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7926,7 +7926,7 @@
         <v>135960754</v>
       </c>
       <c r="B66" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         <v>135960779</v>
       </c>
       <c r="B67" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -8160,7 +8160,7 @@
         <v>135997952</v>
       </c>
       <c r="B68" t="n">
-        <v>57984</v>
+        <v>57985</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -8276,7 +8276,7 @@
         <v>135960753</v>
       </c>
       <c r="B69" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -8393,7 +8393,7 @@
         <v>135961068</v>
       </c>
       <c r="B70" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8510,7 +8510,7 @@
         <v>135997941</v>
       </c>
       <c r="B71" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8627,7 +8627,7 @@
         <v>135997948</v>
       </c>
       <c r="B72" t="n">
-        <v>57174</v>
+        <v>57175</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -9090,7 +9090,7 @@
         <v>135960792</v>
       </c>
       <c r="B76" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -9216,7 +9216,7 @@
         <v>135961072</v>
       </c>
       <c r="B77" t="n">
-        <v>99302</v>
+        <v>99303</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -9333,7 +9333,7 @@
         <v>135960756</v>
       </c>
       <c r="B78" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>135961063</v>
       </c>
       <c r="B79" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -9562,7 +9562,7 @@
         <v>135961066</v>
       </c>
       <c r="B80" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9679,7 +9679,7 @@
         <v>135961084</v>
       </c>
       <c r="B81" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9796,7 +9796,7 @@
         <v>135997947</v>
       </c>
       <c r="B82" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9908,7 +9908,7 @@
         <v>135997953</v>
       </c>
       <c r="B83" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10020,7 +10020,7 @@
         <v>135997958</v>
       </c>
       <c r="B84" t="n">
-        <v>79207</v>
+        <v>79208</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10132,7 +10132,7 @@
         <v>135960790</v>
       </c>
       <c r="B85" t="n">
-        <v>80039</v>
+        <v>80040</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
